--- a/outputs/copper/short/review_summary_file.xlsx
+++ b/outputs/copper/short/review_summary_file.xlsx
@@ -115,16 +115,16 @@
     <t>ARIMA</t>
   </si>
   <si>
+    <t>Random Forest (RF)</t>
+  </si>
+  <si>
+    <t>RF + External Variables</t>
+  </si>
+  <si>
+    <t>Markov-Switching Regression (NEW)</t>
+  </si>
+  <si>
     <t>LGBM + External Variables</t>
-  </si>
-  <si>
-    <t>RF + External Variables</t>
-  </si>
-  <si>
-    <t>Markov-Switching Regression (NEW)</t>
-  </si>
-  <si>
-    <t>Random Forest (RF)</t>
   </si>
   <si>
     <t>LightGBM (LGBM)</t>
@@ -1128,16 +1128,16 @@
         <v>38</v>
       </c>
       <c r="G11">
-        <v>89.94435128205129</v>
+        <v>91.20765897435899</v>
       </c>
       <c r="H11">
-        <v>38.09523571428571</v>
+        <v>42.85715</v>
       </c>
       <c r="I11">
-        <v>24.16822930205096</v>
+        <v>12.0898131026399</v>
       </c>
       <c r="J11">
-        <v>90.05233333333331</v>
+        <v>91.43100000000001</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -1146,7 +1146,7 @@
         <v>0</v>
       </c>
       <c r="M11">
-        <v>67.12649999999999</v>
+        <v>67.2747</v>
       </c>
       <c r="N11">
         <v>9</v>
@@ -1161,7 +1161,7 @@
         <v>0</v>
       </c>
       <c r="R11">
-        <v>9.826428571428574</v>
+        <v>8.266428571428571</v>
       </c>
       <c r="S11">
         <v>14</v>
@@ -1190,16 +1190,16 @@
         <v>38</v>
       </c>
       <c r="G12">
-        <v>90.73461282051281</v>
+        <v>91.09533589743589</v>
       </c>
       <c r="H12">
-        <v>36.90474285714286</v>
+        <v>34.5238</v>
       </c>
       <c r="I12">
-        <v>8.641579108235401</v>
+        <v>9.816839659991498</v>
       </c>
       <c r="J12">
-        <v>90.83166666666665</v>
+        <v>91.18533333333333</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -1208,7 +1208,7 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <v>64.9729</v>
+        <v>64.7697</v>
       </c>
       <c r="N12">
         <v>10</v>
@@ -1223,7 +1223,7 @@
         <v>0</v>
       </c>
       <c r="R12">
-        <v>9.031428571428572</v>
+        <v>8.731428571428571</v>
       </c>
       <c r="S12">
         <v>14</v>
@@ -1314,16 +1314,16 @@
         <v>38</v>
       </c>
       <c r="G14">
-        <v>90.63295641025641</v>
+        <v>89.30865384615386</v>
       </c>
       <c r="H14">
-        <v>23.80951428571429</v>
+        <v>26.19047142857143</v>
       </c>
       <c r="I14">
-        <v>13.51440539190781</v>
+        <v>19.56734731295708</v>
       </c>
       <c r="J14">
-        <v>90.73533333333334</v>
+        <v>89.77366666666668</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="M14">
-        <v>62.3696</v>
+        <v>53.1144</v>
       </c>
       <c r="N14">
         <v>12</v>
@@ -1344,10 +1344,10 @@
         <v>41</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="R14">
-        <v>8.979285714285714</v>
+        <v>10.28428571428571</v>
       </c>
       <c r="S14">
         <v>14</v>
@@ -1376,16 +1376,16 @@
         <v>38</v>
       </c>
       <c r="G15">
-        <v>86.11342564102563</v>
+        <v>86.31777948717949</v>
       </c>
       <c r="H15">
-        <v>16.66665</v>
+        <v>19.04760714285715</v>
       </c>
       <c r="I15">
-        <v>25.46299406650191</v>
+        <v>34.98063514571688</v>
       </c>
       <c r="J15">
-        <v>86.04833333333333</v>
+        <v>86.66766666666668</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -1394,7 +1394,7 @@
         <v>0</v>
       </c>
       <c r="M15">
-        <v>49.6477</v>
+        <v>51.8347</v>
       </c>
       <c r="N15">
         <v>13</v>
@@ -1409,7 +1409,7 @@
         <v>-10</v>
       </c>
       <c r="R15">
-        <v>13.52785714285714</v>
+        <v>13.14857142857143</v>
       </c>
       <c r="S15">
         <v>14</v>
